--- a/data/reports/2024-07-15/2024-07-15_duplicates.xlsx
+++ b/data/reports/2024-07-15/2024-07-15_duplicates.xlsx
@@ -145,7 +145,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=470739ea1bc93c102eb2a82fe54bcba1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004723</t>
+    <t>RMD0005813</t>
   </si>
   <si>
     <t>CoreTel Communications, Inc.</t>
@@ -161,28 +161,28 @@
     <t>Core Communications, Inc., Ton80 Communications, LLC, CoreTel Alabama, Inc., CoreTel Delaware, Inc., CoreTel Florida, Inc., CoreTel Georgia, Inc., CoreTel Kansas, Inc., CoreTel Kentucky, Inc., CoreTel Massachusetts, Inc., CoreTel New Jersey, Inc., CoreTel Virginia, Inc., CoreTel West Virginia, Inc., CoreTel Washington, Inc.,</t>
   </si>
   <si>
+    <t>Glenn Dalgliesh</t>
+  </si>
+  <si>
+    <t>VP of Operations</t>
+  </si>
+  <si>
+    <t>NOC</t>
+  </si>
+  <si>
+    <t>'+14439121000</t>
+  </si>
+  <si>
+    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004723</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=0df870c21bcdf41002beea82f54bcba2&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005813</t>
-  </si>
-  <si>
-    <t>Glenn Dalgliesh</t>
-  </si>
-  <si>
-    <t>VP of Operations</t>
-  </si>
-  <si>
-    <t>NOC</t>
-  </si>
-  <si>
-    <t>'+14439121000</t>
-  </si>
-  <si>
-    <t>Partial STIR/SHAKEN Implementation - Performing Robocall Mitigation</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=34a57d161b667c10dabd2f41f54bcb14&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004139</t>
@@ -225,10 +225,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b379943f1be37810cc2f2f82f54bcbf5&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008972</t>
+  </si>
+  <si>
+    <t>Media Flint, Inc.</t>
+  </si>
+  <si>
+    <t>15260 Ventura Boulevard
+Suite 1200 PMB 492
+Sherman Oaks California 91403</t>
+  </si>
+  <si>
+    <t>U.S. Virgin Islands</t>
+  </si>
+  <si>
+    <t>AvidTrak</t>
+  </si>
+  <si>
+    <t>null
+null CA
+California</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008973</t>
-  </si>
-  <si>
-    <t>Media Flint, Inc.</t>
   </si>
   <si>
     <t>15260 Ventura Boulevard
@@ -236,32 +258,10 @@
 Sherman Oaks CA 91403</t>
   </si>
   <si>
-    <t>U.S. Virgin Islands</t>
-  </si>
-  <si>
-    <t>AvidTrak</t>
-  </si>
-  <si>
-    <t>null
-null CA
-California</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bfc7bfc81b9f74505eb762cfe54bcbe5&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008972</t>
-  </si>
-  <si>
-    <t>15260 Ventura Boulevard
-Suite 1200 PMB 492
-Sherman Oaks California 91403</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=26b57f081b9f74505eb762cfe54bcb14&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009020</t>
+    <t>RMD0009019</t>
   </si>
   <si>
     <t>Enhanced Telecommunications &amp; Data, Inc.</t>
@@ -277,6 +277,24 @@
     <t>Engineer</t>
   </si>
   <si>
+    <t>IT</t>
+  </si>
+  <si>
+    <t>208-947-3900</t>
+  </si>
+  <si>
+    <t>3904</t>
+  </si>
+  <si>
+    <t>2024-04-09</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009020</t>
+  </si>
+  <si>
     <t>IT Department</t>
   </si>
   <si>
@@ -286,25 +304,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=bcd785dd1b17f010222b0e9ee54bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009019</t>
-  </si>
-  <si>
-    <t>IT</t>
-  </si>
-  <si>
-    <t>208-947-3900</t>
-  </si>
-  <si>
-    <t>3904</t>
-  </si>
-  <si>
-    <t>2024-04-09</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5e6e01191b57f010222b0e9ee54bcb7a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0009205</t>
+    <t>RMD0009084</t>
   </si>
   <si>
     <t>ADCOM Technologies, LLC</t>
@@ -318,6 +318,12 @@
     <t>ON DEMAND Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0009205</t>
+  </si>
+  <si>
     <t>Dean Franks</t>
   </si>
   <si>
@@ -340,13 +346,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=53ad1e731b53b0109294113d9c4bcb6a&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0009084</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=fd73904e1b1bf010031f0f21f54bcb87&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008869</t>
+    <t>RMD0006774</t>
   </si>
   <si>
     <t>Sage Communications, Inc.</t>
@@ -356,9 +356,18 @@
 Camarillo CA 93012</t>
   </si>
   <si>
+    <t>NONE</t>
+  </si>
+  <si>
     <t>Sage Network &amp; Communications</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008869</t>
+  </si>
+  <si>
     <t>Rick Minyard</t>
   </si>
   <si>
@@ -378,15 +387,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ed3d8a531b0334509ac2ea04bc4bcb27&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0006774</t>
-  </si>
-  <si>
-    <t>NONE</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612a08851bbef010e1ca848ce54bcbb3&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0004389</t>
@@ -469,10 +469,20 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1f0635261b85f81002beea82f54bcbec&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0005785</t>
+  </si>
+  <si>
+    <t>Edge Fibernet</t>
+  </si>
+  <si>
+    <t>5004 4th Avenue
+Brooklyn New York 11220</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0005786</t>
-  </si>
-  <si>
-    <t>Edge Fibernet</t>
   </si>
   <si>
     <t>254 36th Street
@@ -483,16 +493,6 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=eb20864e1bea3c105e240f6fe54bcbf1&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005785</t>
-  </si>
-  <si>
-    <t>5004 4th Avenue
-Brooklyn New York 11220</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5dcfb14e1bea3c105e240f6fe54bcb62&amp;view=sp</t>
-  </si>
-  <si>
     <t>RMD0007488</t>
   </si>
   <si>
@@ -596,7 +596,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=89cc84f51b4af01068d1a82eac4bcb3e&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0004701</t>
+    <t>RMD0003052</t>
   </si>
   <si>
     <t>Jaintel LLC</t>
@@ -606,15 +606,33 @@
 DE 19806-3334 Wilmington, United States</t>
   </si>
   <si>
+    <t>United Kingdom</t>
+  </si>
+  <si>
     <t>Elayaraja Jinadoss</t>
   </si>
   <si>
+    <t>Director</t>
+  </si>
+  <si>
+    <t>Management</t>
+  </si>
+  <si>
+    <t>'+447341664829</t>
+  </si>
+  <si>
+    <t>2024-05-01</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0004701</t>
+  </si>
+  <si>
     <t>Operations Director</t>
   </si>
   <si>
-    <t>Management</t>
-  </si>
-  <si>
     <t>'+1 737 237 0913</t>
   </si>
   <si>
@@ -622,24 +640,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b1f3904a1b4138107ccf20ecac4bcbbf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003052</t>
-  </si>
-  <si>
-    <t>United Kingdom</t>
-  </si>
-  <si>
-    <t>Director</t>
-  </si>
-  <si>
-    <t>'+447341664829</t>
-  </si>
-  <si>
-    <t>2024-05-01</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=296153731b30b0507ccf20ecac4bcbd8&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0003053</t>
@@ -670,7 +670,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1e7857331b4885103e8aa93be54bcb79&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0003444</t>
+    <t>RMD0003442</t>
   </si>
   <si>
     <t>Shaw Telecom GP</t>
@@ -681,32 +681,6 @@
   </si>
   <si>
     <t>Canada</t>
-  </si>
-  <si>
-    <t>0031064868; 0031064884; 0031064900</t>
-  </si>
-  <si>
-    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
-  </si>
-  <si>
-    <t>Network Operations</t>
-  </si>
-  <si>
-    <t>TOPS-NR&amp;A</t>
-  </si>
-  <si>
-    <t>2728 Hopewell Place N.E.
-Calgary AE 17724
-Alberta</t>
-  </si>
-  <si>
-    <t>'+1-866-244-7475</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0003442</t>
   </si>
   <si>
     <t>0031064868;
@@ -726,6 +700,32 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=322c4e941b8df0509294113d9c4bcb51&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0003444</t>
+  </si>
+  <si>
+    <t>0031064868; 0031064884; 0031064900</t>
+  </si>
+  <si>
+    <t>SHAW CORP; 1503357 Alberta Ltd.; 1950036 Ontario Ltd.; Mid-Bowline Group Corp.; Mid-Bowline Holdings Corp.; Wind Mobile Corp.; Freedom Mobile Inc.</t>
+  </si>
+  <si>
+    <t>Network Operations</t>
+  </si>
+  <si>
+    <t>TOPS-NR&amp;A</t>
+  </si>
+  <si>
+    <t>2728 Hopewell Place N.E.
+Calgary AE 17724
+Alberta</t>
+  </si>
+  <si>
+    <t>'+1-866-244-7475</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=5d9f0e581b8df0509294113d9c4bcb95&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0007384</t>
   </si>
   <si>
@@ -754,7 +754,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=76af51511bc9f0102eb2a82fe54bcb18&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008577</t>
+    <t>RMD0005040</t>
   </si>
   <si>
     <t>Dialect, LLC</t>
@@ -764,6 +764,12 @@
 Phoenix AZ 85008</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0008577</t>
+  </si>
+  <si>
     <t>BatchDialer</t>
   </si>
   <si>
@@ -780,12 +786,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=ee4909b01b8f7c10aa3cea41f54bcb77&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005040</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=f58908e11b793c10680f657ae54bcb6d&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0005569</t>
@@ -836,7 +836,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=612913461bd6f010ca5aec21f54bcbac&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007936</t>
+    <t>RMD0005297</t>
   </si>
   <si>
     <t>STREAMLINE SELLERS PTY LTD</t>
@@ -849,6 +849,12 @@
     <t>Australia</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007936</t>
+  </si>
+  <si>
     <t>Syed Omar Farooq Shah</t>
   </si>
   <si>
@@ -858,13 +864,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=6273a2321b3638109ac2ea04bc4bcb55&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0005297</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d24a9a271bca3810d49ca86ce54bcb20&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005585</t>
+    <t>RMD0005574</t>
   </si>
   <si>
     <t>MegaClec, Inc</t>
@@ -878,6 +878,22 @@
     <t>0012465480</t>
   </si>
   <si>
+    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
+  </si>
+  <si>
+    <t>187 Plymouth Ave
+Fall River MA 02721</t>
+  </si>
+  <si>
+    <t>5086460030</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0005585</t>
+  </si>
+  <si>
     <t>Voiceay, Voiceway Netoworks, Meganet,  Troy City Internet Exchange</t>
   </si>
   <si>
@@ -891,23 +907,7 @@
 Fall River MA 02721</t>
   </si>
   <si>
-    <t>5086460030</t>
-  </si>
-  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c9f5735c1ba2781002beea82f54bcbaf&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0005574</t>
-  </si>
-  <si>
-    <t>Troy City Internet Exchange;Voiceway;Meganet Communications</t>
-  </si>
-  <si>
-    <t>187 Plymouth Ave
-Fall River MA 02721</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=1426e7581ba678109294113d9c4bcb2f&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0007962</t>
@@ -993,7 +993,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=cfeb296a1bf6f410680f657ae54bcbeb&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007696</t>
+    <t>RMD0007716</t>
   </si>
   <si>
     <t>High Country Internet</t>
@@ -1003,16 +1003,16 @@
 Tucson AZ 85719</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007696</t>
+  </si>
+  <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=e3d356aa1b3ef410165aedfde54bcb51&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0007716</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=4a516ea21b7ef410165aedfde54bcbd3&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007944</t>
+    <t>RMD0007939</t>
   </si>
   <si>
     <t>Conquest Solutions</t>
@@ -1022,6 +1022,12 @@
 Marietta GA 30067</t>
   </si>
   <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
+  </si>
+  <si>
+    <t>RMD0007944</t>
+  </si>
+  <si>
     <t>Lance Retter</t>
   </si>
   <si>
@@ -1035,12 +1041,6 @@
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=c186e6321bba3810e4ccdb1de54bcb5a&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0007939</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d225a2fe1b7a3810e4ccdb1de54bcbff&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008423</t>
@@ -1074,7 +1074,7 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=545854ef1b7ab810d39dddb6bc4bcb74&amp;view=sp</t>
   </si>
   <si>
-    <t>RMD0008451</t>
+    <t>RMD0008450</t>
   </si>
   <si>
     <t>WTS</t>
@@ -1084,12 +1084,6 @@
 Greensboro NC 27401</t>
   </si>
   <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008450</t>
-  </si>
-  <si>
     <t>null
 null NC</t>
   </si>
@@ -1097,6 +1091,12 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=b746a9e71bbeb81093d3a820f54bcb4c&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008451</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=d7e7ad2b1bbeb81093d3a820f54bcb5c&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008611</t>
   </si>
   <si>
@@ -1116,25 +1116,25 @@
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=8ce1e5851b0bbc1093d3a820f54bcba5&amp;view=sp</t>
   </si>
   <si>
+    <t>RMD0008612</t>
+  </si>
+  <si>
+    <t>India</t>
+  </si>
+  <si>
+    <t>Bharat Raj</t>
+  </si>
+  <si>
+    <t>'+919836963636</t>
+  </si>
+  <si>
+    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
+  </si>
+  <si>
     <t>RMD0008610</t>
   </si>
   <si>
     <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=9c9129851b0bbc1093d3a820f54bcb97&amp;view=sp</t>
-  </si>
-  <si>
-    <t>RMD0008612</t>
-  </si>
-  <si>
-    <t>India</t>
-  </si>
-  <si>
-    <t>Bharat Raj</t>
-  </si>
-  <si>
-    <t>'+919836963636</t>
-  </si>
-  <si>
-    <t>https://fccprod.servicenowservices.com/rmd?id=rmd_form&amp;table=x_g_fmc_rmd_robocall_mitigation_database&amp;sys_id=21f229c51b0bbc1093d3a820f54bcbdb&amp;view=sp</t>
   </si>
   <si>
     <t>RMD0008759</t>
@@ -6247,16 +6247,28 @@
         <v>46</v>
       </c>
       <c r="I5" s="1"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="J5" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>49</v>
+      </c>
       <c r="M5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N5" s="1"/>
-      <c r="O5" s="1"/>
+        <v>44</v>
+      </c>
+      <c r="N5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O5" s="1" t="s">
+        <v>50</v>
+      </c>
       <c r="P5" s="1"/>
-      <c r="Q5" s="1"/>
+      <c r="Q5" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R5" s="1" t="s">
         <v>26</v>
       </c>
@@ -6264,16 +6276,16 @@
         <v>26</v>
       </c>
       <c r="T5" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U5" s="1"/>
       <c r="V5" s="1" t="s">
-        <v>47</v>
+        <v>52</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="1" t="s">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="B6" s="1">
         <v>17118795</v>
@@ -6297,28 +6309,16 @@
         <v>46</v>
       </c>
       <c r="I6" s="1"/>
-      <c r="J6" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>51</v>
-      </c>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
       <c r="M6" s="1" t="s">
-        <v>44</v>
-      </c>
-      <c r="N6" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O6" s="1" t="s">
-        <v>52</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
       <c r="P6" s="1"/>
-      <c r="Q6" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q6" s="1"/>
       <c r="R6" s="1" t="s">
         <v>26</v>
       </c>
@@ -6326,7 +6326,7 @@
         <v>26</v>
       </c>
       <c r="T6" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U6" s="1"/>
       <c r="V6" s="1" t="s">
@@ -6595,9 +6595,11 @@
       <c r="O11" s="1" t="s">
         <v>84</v>
       </c>
-      <c r="P11" s="1"/>
+      <c r="P11" s="1" t="s">
+        <v>85</v>
+      </c>
       <c r="Q11" s="1" t="s">
-        <v>53</v>
+        <v>39</v>
       </c>
       <c r="R11" s="1" t="s">
         <v>30</v>
@@ -6608,14 +6610,16 @@
       <c r="T11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U11" s="1"/>
+      <c r="U11" s="1" t="s">
+        <v>86</v>
+      </c>
       <c r="V11" s="1" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="B12" s="1">
         <v>21520390</v>
@@ -6642,7 +6646,7 @@
         <v>82</v>
       </c>
       <c r="L12" s="1" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M12" s="1" t="s">
         <v>80</v>
@@ -6651,13 +6655,11 @@
         <v>27</v>
       </c>
       <c r="O12" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="P12" s="1" t="s">
-        <v>89</v>
-      </c>
+        <v>90</v>
+      </c>
+      <c r="P12" s="1"/>
       <c r="Q12" s="1" t="s">
-        <v>39</v>
+        <v>51</v>
       </c>
       <c r="R12" s="1" t="s">
         <v>30</v>
@@ -6668,9 +6670,7 @@
       <c r="T12" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="U12" s="1" t="s">
-        <v>90</v>
-      </c>
+      <c r="U12" s="1"/>
       <c r="V12" s="1" t="s">
         <v>91</v>
       </c>
@@ -6689,55 +6689,41 @@
         <v>94</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G13" s="1"/>
       <c r="H13" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I13" s="1"/>
-      <c r="J13" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="M13" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="N13" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O13" s="1" t="s">
-        <v>100</v>
-      </c>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
+      <c r="N13" s="1"/>
+      <c r="O13" s="1"/>
       <c r="P13" s="1"/>
-      <c r="Q13" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q13" s="1"/>
       <c r="R13" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S13" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T13" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U13" s="1"/>
       <c r="V13" s="1" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="14" spans="1:22">
       <c r="A14" s="1" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="B14" s="1">
         <v>23003460</v>
@@ -6749,32 +6735,46 @@
         <v>94</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
         <v>95</v>
       </c>
       <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
-      <c r="N14" s="1"/>
-      <c r="O14" s="1"/>
+      <c r="J14" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>99</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>100</v>
+      </c>
+      <c r="M14" s="1" t="s">
+        <v>101</v>
+      </c>
+      <c r="N14" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O14" s="1" t="s">
+        <v>102</v>
+      </c>
       <c r="P14" s="1"/>
-      <c r="Q14" s="1"/>
+      <c r="Q14" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R14" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S14" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T14" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U14" s="1"/>
       <c r="V14" s="1" t="s">
@@ -6800,54 +6800,40 @@
       <c r="F15" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G15" s="1"/>
+      <c r="G15" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="H15" s="1" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I15" s="1"/>
-      <c r="J15" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="K15" s="1" t="s">
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="N15" s="1"/>
+      <c r="O15" s="1"/>
+      <c r="P15" s="1"/>
+      <c r="Q15" s="1"/>
+      <c r="R15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="S15" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="U15" s="1"/>
+      <c r="V15" s="1" t="s">
         <v>110</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>111</v>
-      </c>
-      <c r="M15" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="N15" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O15" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="P15" s="1" t="s">
-        <v>113</v>
-      </c>
-      <c r="Q15" s="1" t="s">
-        <v>39</v>
-      </c>
-      <c r="R15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="S15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T15" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U15" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="V15" s="1" t="s">
-        <v>115</v>
       </c>
     </row>
     <row r="16" spans="1:22">
       <c r="A16" s="1" t="s">
-        <v>116</v>
+        <v>111</v>
       </c>
       <c r="B16" s="1">
         <v>23250467</v>
@@ -6864,33 +6850,47 @@
       <c r="F16" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="1"/>
+      <c r="H16" s="1" t="s">
+        <v>109</v>
+      </c>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1" t="s">
+        <v>112</v>
+      </c>
+      <c r="K16" s="1" t="s">
+        <v>113</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>107</v>
+      </c>
+      <c r="N16" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O16" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="P16" s="1" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q16" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="R16" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="S16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="T16" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="U16" s="1" t="s">
         <v>117</v>
       </c>
-      <c r="H16" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="1"/>
-      <c r="L16" s="1"/>
-      <c r="M16" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N16" s="1"/>
-      <c r="O16" s="1"/>
-      <c r="P16" s="1"/>
-      <c r="Q16" s="1"/>
-      <c r="R16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="S16" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="T16" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U16" s="1"/>
       <c r="V16" s="1" t="s">
         <v>118</v>
       </c>
@@ -7056,13 +7056,13 @@
       <c r="H20" s="1"/>
       <c r="I20" s="1"/>
       <c r="J20" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="K20" s="1" t="s">
+        <v>48</v>
+      </c>
+      <c r="L20" s="1" t="s">
         <v>49</v>
-      </c>
-      <c r="K20" s="1" t="s">
-        <v>50</v>
-      </c>
-      <c r="L20" s="1" t="s">
-        <v>51</v>
       </c>
       <c r="M20" s="1" t="s">
         <v>127</v>
@@ -7075,7 +7075,7 @@
       </c>
       <c r="P20" s="1"/>
       <c r="Q20" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R20" s="1" t="s">
         <v>26</v>
@@ -7393,7 +7393,7 @@
       </c>
       <c r="P26" s="1"/>
       <c r="Q26" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R26" s="1" t="s">
         <v>26</v>
@@ -7541,55 +7541,61 @@
         <v>184</v>
       </c>
       <c r="E29" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="G29" s="1"/>
-      <c r="H29" s="1"/>
-      <c r="I29" s="1"/>
+        <v>185</v>
+      </c>
+      <c r="G29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="H29" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="I29" s="1" t="s">
+        <v>108</v>
+      </c>
       <c r="J29" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K29" s="1" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="L29" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M29" s="1" t="s">
         <v>184</v>
       </c>
       <c r="N29" s="1" t="s">
-        <v>27</v>
+        <v>185</v>
       </c>
       <c r="O29" s="1" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="P29" s="1"/>
       <c r="Q29" s="1" t="s">
         <v>39</v>
       </c>
       <c r="R29" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S29" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="T29" s="1" t="s">
         <v>26</v>
       </c>
       <c r="U29" s="1" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="V29" s="1" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="1" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="B30" s="1">
         <v>30758643</v>
@@ -7601,34 +7607,28 @@
         <v>184</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>192</v>
-      </c>
-      <c r="G30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="H30" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="I30" s="1" t="s">
-        <v>117</v>
-      </c>
+        <v>27</v>
+      </c>
+      <c r="G30" s="1"/>
+      <c r="H30" s="1"/>
+      <c r="I30" s="1"/>
       <c r="J30" s="1" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="K30" s="1" t="s">
         <v>193</v>
       </c>
       <c r="L30" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M30" s="1" t="s">
         <v>184</v>
       </c>
       <c r="N30" s="1" t="s">
-        <v>192</v>
+        <v>27</v>
       </c>
       <c r="O30" s="1" t="s">
         <v>194</v>
@@ -7638,10 +7638,10 @@
         <v>39</v>
       </c>
       <c r="R30" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S30" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="T30" s="1" t="s">
         <v>26</v>
@@ -7670,7 +7670,7 @@
         <v>30</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G31" s="1"/>
       <c r="H31" s="1"/>
@@ -7716,7 +7716,7 @@
         <v>30</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G32" s="1"/>
       <c r="H32" s="1"/>
@@ -7734,14 +7734,14 @@
         <v>199</v>
       </c>
       <c r="N32" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O32" s="1" t="s">
         <v>204</v>
       </c>
       <c r="P32" s="1"/>
       <c r="Q32" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R32" s="1" t="s">
         <v>30</v>
@@ -7783,45 +7783,33 @@
       <c r="I33" s="1" t="s">
         <v>211</v>
       </c>
-      <c r="J33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="K33" s="1" t="s">
-        <v>212</v>
-      </c>
-      <c r="L33" s="1" t="s">
-        <v>213</v>
-      </c>
+      <c r="J33" s="1"/>
+      <c r="K33" s="1"/>
+      <c r="L33" s="1"/>
       <c r="M33" s="1" t="s">
-        <v>214</v>
-      </c>
-      <c r="N33" s="1" t="s">
-        <v>209</v>
-      </c>
-      <c r="O33" s="1" t="s">
-        <v>215</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N33" s="1"/>
+      <c r="O33" s="1"/>
       <c r="P33" s="1"/>
-      <c r="Q33" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q33" s="1"/>
       <c r="R33" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S33" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T33" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U33" s="1"/>
       <c r="V33" s="1" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="34" spans="1:22">
       <c r="A34" s="1" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="B34" s="1">
         <v>31064850</v>
@@ -7839,30 +7827,42 @@
         <v>209</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="H34" s="1"/>
       <c r="I34" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="J34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="K34" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="L34" s="1" t="s">
+        <v>217</v>
+      </c>
+      <c r="M34" s="1" t="s">
+        <v>218</v>
+      </c>
+      <c r="N34" s="1" t="s">
+        <v>209</v>
+      </c>
+      <c r="O34" s="1" t="s">
         <v>219</v>
       </c>
-      <c r="J34" s="1"/>
-      <c r="K34" s="1"/>
-      <c r="L34" s="1"/>
-      <c r="M34" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N34" s="1"/>
-      <c r="O34" s="1"/>
       <c r="P34" s="1"/>
-      <c r="Q34" s="1"/>
+      <c r="Q34" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R34" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S34" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T34" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U34" s="1"/>
       <c r="V34" s="1" t="s">
@@ -7911,7 +7911,7 @@
       </c>
       <c r="P35" s="1"/>
       <c r="Q35" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R35" s="1" t="s">
         <v>30</v>
@@ -7994,48 +7994,34 @@
       </c>
       <c r="G37" s="1"/>
       <c r="H37" s="1"/>
-      <c r="I37" s="1" t="s">
-        <v>233</v>
-      </c>
-      <c r="J37" s="1" t="s">
-        <v>234</v>
-      </c>
-      <c r="K37" s="1" t="s">
-        <v>235</v>
-      </c>
-      <c r="L37" s="1" t="s">
-        <v>236</v>
-      </c>
+      <c r="I37" s="1"/>
+      <c r="J37" s="1"/>
+      <c r="K37" s="1"/>
+      <c r="L37" s="1"/>
       <c r="M37" s="1" t="s">
-        <v>232</v>
-      </c>
-      <c r="N37" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O37" s="1" t="s">
-        <v>237</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N37" s="1"/>
+      <c r="O37" s="1"/>
       <c r="P37" s="1"/>
-      <c r="Q37" s="1" t="s">
-        <v>53</v>
-      </c>
+      <c r="Q37" s="1"/>
       <c r="R37" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S37" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T37" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U37" s="1"/>
       <c r="V37" s="1" t="s">
-        <v>238</v>
+        <v>233</v>
       </c>
     </row>
     <row r="38" spans="1:22">
       <c r="A38" s="1" t="s">
-        <v>239</v>
+        <v>234</v>
       </c>
       <c r="B38" s="1">
         <v>31124688</v>
@@ -8054,25 +8040,39 @@
       </c>
       <c r="G38" s="1"/>
       <c r="H38" s="1"/>
-      <c r="I38" s="1"/>
-      <c r="J38" s="1"/>
-      <c r="K38" s="1"/>
-      <c r="L38" s="1"/>
+      <c r="I38" s="1" t="s">
+        <v>235</v>
+      </c>
+      <c r="J38" s="1" t="s">
+        <v>236</v>
+      </c>
+      <c r="K38" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="L38" s="1" t="s">
+        <v>238</v>
+      </c>
       <c r="M38" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N38" s="1"/>
-      <c r="O38" s="1"/>
+        <v>232</v>
+      </c>
+      <c r="N38" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O38" s="1" t="s">
+        <v>239</v>
+      </c>
       <c r="P38" s="1"/>
-      <c r="Q38" s="1"/>
+      <c r="Q38" s="1" t="s">
+        <v>51</v>
+      </c>
       <c r="R38" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S38" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T38" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U38" s="1"/>
       <c r="V38" s="1" t="s">
@@ -8121,7 +8121,7 @@
       </c>
       <c r="P39" s="1"/>
       <c r="Q39" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R39" s="1" t="s">
         <v>26</v>
@@ -8223,45 +8223,33 @@
       <c r="G41" s="1"/>
       <c r="H41" s="1"/>
       <c r="I41" s="1"/>
-      <c r="J41" s="1" t="s">
-        <v>260</v>
-      </c>
-      <c r="K41" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L41" s="1" t="s">
-        <v>203</v>
-      </c>
+      <c r="J41" s="1"/>
+      <c r="K41" s="1"/>
+      <c r="L41" s="1"/>
       <c r="M41" s="1" t="s">
-        <v>258</v>
-      </c>
-      <c r="N41" s="1" t="s">
-        <v>259</v>
-      </c>
-      <c r="O41" s="1" t="s">
-        <v>261</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N41" s="1"/>
+      <c r="O41" s="1"/>
       <c r="P41" s="1"/>
-      <c r="Q41" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q41" s="1"/>
       <c r="R41" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S41" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T41" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U41" s="1"/>
       <c r="V41" s="1" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="42" spans="1:22">
       <c r="A42" s="1" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="B42" s="1">
         <v>31294614</v>
@@ -8281,24 +8269,36 @@
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
       <c r="I42" s="1"/>
-      <c r="J42" s="1"/>
-      <c r="K42" s="1"/>
-      <c r="L42" s="1"/>
+      <c r="J42" s="1" t="s">
+        <v>262</v>
+      </c>
+      <c r="K42" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L42" s="1" t="s">
+        <v>203</v>
+      </c>
       <c r="M42" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N42" s="1"/>
-      <c r="O42" s="1"/>
+        <v>258</v>
+      </c>
+      <c r="N42" s="1" t="s">
+        <v>259</v>
+      </c>
+      <c r="O42" s="1" t="s">
+        <v>263</v>
+      </c>
       <c r="P42" s="1"/>
-      <c r="Q42" s="1"/>
+      <c r="Q42" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R42" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S42" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T42" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U42" s="1"/>
       <c r="V42" s="1" t="s">
@@ -8330,48 +8330,42 @@
       <c r="H43" s="1" t="s">
         <v>269</v>
       </c>
-      <c r="I43" s="1"/>
-      <c r="J43" s="1" t="s">
+      <c r="I43" s="1" t="s">
+        <v>108</v>
+      </c>
+      <c r="J43" s="1"/>
+      <c r="K43" s="1"/>
+      <c r="L43" s="1"/>
+      <c r="M43" s="1" t="s">
         <v>270</v>
       </c>
-      <c r="K43" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="L43" s="1" t="s">
+      <c r="N43" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O43" s="1" t="s">
         <v>271</v>
-      </c>
-      <c r="M43" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="N43" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O43" s="1" t="s">
-        <v>273</v>
       </c>
       <c r="P43" s="1"/>
       <c r="Q43" s="1" t="s">
-        <v>39</v>
+        <v>103</v>
       </c>
       <c r="R43" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S43" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T43" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="U43" s="1" t="s">
-        <v>62</v>
-      </c>
+        <v>30</v>
+      </c>
+      <c r="U43" s="1"/>
       <c r="V43" s="1" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
     </row>
     <row r="44" spans="1:22">
       <c r="A44" s="1" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="B44" s="1">
         <v>31356652</v>
@@ -8392,14 +8386,18 @@
         <v>268</v>
       </c>
       <c r="H44" s="1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I44" s="1"/>
+      <c r="J44" s="1" t="s">
+        <v>275</v>
+      </c>
+      <c r="K44" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="L44" s="1" t="s">
         <v>276</v>
       </c>
-      <c r="I44" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="J44" s="1"/>
-      <c r="K44" s="1"/>
-      <c r="L44" s="1"/>
       <c r="M44" s="1" t="s">
         <v>277</v>
       </c>
@@ -8407,22 +8405,24 @@
         <v>27</v>
       </c>
       <c r="O44" s="1" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="P44" s="1"/>
       <c r="Q44" s="1" t="s">
-        <v>101</v>
+        <v>39</v>
       </c>
       <c r="R44" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S44" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T44" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="U44" s="1"/>
+        <v>26</v>
+      </c>
+      <c r="U44" s="1" t="s">
+        <v>62</v>
+      </c>
       <c r="V44" s="1" t="s">
         <v>278</v>
       </c>
@@ -8467,7 +8467,7 @@
       </c>
       <c r="P45" s="1"/>
       <c r="Q45" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R45" s="1" t="s">
         <v>30</v>
@@ -8748,9 +8748,15 @@
       <c r="F51" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G51" s="1"/>
-      <c r="H51" s="1"/>
-      <c r="I51" s="1"/>
+      <c r="G51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="H51" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="I51" s="1" t="s">
+        <v>28</v>
+      </c>
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
@@ -8794,15 +8800,9 @@
       <c r="F52" s="1" t="s">
         <v>71</v>
       </c>
-      <c r="G52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="H52" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="I52" s="1" t="s">
-        <v>28</v>
-      </c>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
@@ -8841,55 +8841,41 @@
         <v>313</v>
       </c>
       <c r="E53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>27</v>
+        <v>71</v>
       </c>
       <c r="G53" s="1"/>
       <c r="H53" s="1"/>
       <c r="I53" s="1"/>
-      <c r="J53" s="1" t="s">
-        <v>314</v>
-      </c>
-      <c r="K53" s="1" t="s">
-        <v>315</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>87</v>
-      </c>
+      <c r="J53" s="1"/>
+      <c r="K53" s="1"/>
+      <c r="L53" s="1"/>
       <c r="M53" s="1" t="s">
-        <v>313</v>
-      </c>
-      <c r="N53" s="1" t="s">
-        <v>27</v>
-      </c>
-      <c r="O53" s="1" t="s">
-        <v>316</v>
-      </c>
-      <c r="P53" s="1" t="s">
-        <v>317</v>
-      </c>
-      <c r="Q53" s="1" t="s">
-        <v>39</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N53" s="1"/>
+      <c r="O53" s="1"/>
+      <c r="P53" s="1"/>
+      <c r="Q53" s="1"/>
       <c r="R53" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S53" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T53" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U53" s="1"/>
       <c r="V53" s="1" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
     </row>
     <row r="54" spans="1:22">
       <c r="A54" s="1" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="B54" s="1">
         <v>31445216</v>
@@ -8901,32 +8887,46 @@
         <v>313</v>
       </c>
       <c r="E54" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>71</v>
+        <v>27</v>
       </c>
       <c r="G54" s="1"/>
       <c r="H54" s="1"/>
       <c r="I54" s="1"/>
-      <c r="J54" s="1"/>
-      <c r="K54" s="1"/>
-      <c r="L54" s="1"/>
+      <c r="J54" s="1" t="s">
+        <v>316</v>
+      </c>
+      <c r="K54" s="1" t="s">
+        <v>317</v>
+      </c>
+      <c r="L54" s="1" t="s">
+        <v>83</v>
+      </c>
       <c r="M54" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N54" s="1"/>
-      <c r="O54" s="1"/>
-      <c r="P54" s="1"/>
-      <c r="Q54" s="1"/>
+        <v>313</v>
+      </c>
+      <c r="N54" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="O54" s="1" t="s">
+        <v>318</v>
+      </c>
+      <c r="P54" s="1" t="s">
+        <v>319</v>
+      </c>
+      <c r="Q54" s="1" t="s">
+        <v>39</v>
+      </c>
       <c r="R54" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S54" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T54" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U54" s="1"/>
       <c r="V54" s="1" t="s">
@@ -9061,7 +9061,7 @@
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1" t="s">
-        <v>29</v>
+        <v>333</v>
       </c>
       <c r="N57" s="1"/>
       <c r="O57" s="1"/>
@@ -9078,12 +9078,12 @@
       </c>
       <c r="U57" s="1"/>
       <c r="V57" s="1" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
     </row>
     <row r="58" spans="1:22">
       <c r="A58" s="1" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="B58" s="1">
         <v>31457815</v>
@@ -9107,7 +9107,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1" t="s">
-        <v>335</v>
+        <v>29</v>
       </c>
       <c r="N58" s="1"/>
       <c r="O58" s="1"/>
@@ -9192,38 +9192,50 @@
         <v>30</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="G60" s="1"/>
       <c r="H60" s="1"/>
       <c r="I60" s="1"/>
-      <c r="J60" s="1"/>
-      <c r="K60" s="1"/>
-      <c r="L60" s="1"/>
+      <c r="J60" s="1" t="s">
+        <v>345</v>
+      </c>
+      <c r="K60" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="L60" s="1" t="s">
+        <v>37</v>
+      </c>
       <c r="M60" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="N60" s="1"/>
-      <c r="O60" s="1"/>
+        <v>339</v>
+      </c>
+      <c r="N60" s="1" t="s">
+        <v>344</v>
+      </c>
+      <c r="O60" s="1" t="s">
+        <v>346</v>
+      </c>
       <c r="P60" s="1"/>
-      <c r="Q60" s="1"/>
+      <c r="Q60" s="1" t="s">
+        <v>103</v>
+      </c>
       <c r="R60" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="S60" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T60" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="U60" s="1"/>
       <c r="V60" s="1" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
     </row>
     <row r="61" spans="1:22">
       <c r="A61" s="1" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="B61" s="1">
         <v>31475270</v>
@@ -9238,41 +9250,29 @@
         <v>30</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="G61" s="1"/>
       <c r="H61" s="1"/>
       <c r="I61" s="1"/>
-      <c r="J61" s="1" t="s">
-        <v>347</v>
-      </c>
-      <c r="K61" s="1" t="s">
-        <v>193</v>
-      </c>
-      <c r="L61" s="1" t="s">
-        <v>37</v>
-      </c>
+      <c r="J61" s="1"/>
+      <c r="K61" s="1"/>
+      <c r="L61" s="1"/>
       <c r="M61" s="1" t="s">
-        <v>339</v>
-      </c>
-      <c r="N61" s="1" t="s">
-        <v>346</v>
-      </c>
-      <c r="O61" s="1" t="s">
-        <v>348</v>
-      </c>
+        <v>29</v>
+      </c>
+      <c r="N61" s="1"/>
+      <c r="O61" s="1"/>
       <c r="P61" s="1"/>
-      <c r="Q61" s="1" t="s">
-        <v>101</v>
-      </c>
+      <c r="Q61" s="1"/>
       <c r="R61" s="1" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="S61" s="1" t="s">
         <v>26</v>
       </c>
       <c r="T61" s="1" t="s">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="U61" s="1"/>
       <c r="V61" s="1" t="s">
@@ -9319,7 +9319,7 @@
         <v>354</v>
       </c>
       <c r="Q62" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R62" s="1" t="s">
         <v>30</v>
@@ -9425,7 +9425,7 @@
         <v>366</v>
       </c>
       <c r="Q64" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R64" s="1" t="s">
         <v>30</v>
@@ -9783,7 +9783,7 @@
       </c>
       <c r="P71" s="1"/>
       <c r="Q71" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R71" s="1" t="s">
         <v>30</v>
@@ -9885,7 +9885,7 @@
       </c>
       <c r="P73" s="1"/>
       <c r="Q73" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R73" s="1" t="s">
         <v>30</v>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="P74" s="1"/>
       <c r="Q74" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R74" s="1" t="s">
         <v>30</v>
@@ -10044,7 +10044,7 @@
         <v>59</v>
       </c>
       <c r="L76" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M76" s="1" t="s">
         <v>423</v>
@@ -10057,7 +10057,7 @@
       </c>
       <c r="P76" s="1"/>
       <c r="Q76" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R76" s="1" t="s">
         <v>30</v>
@@ -10119,7 +10119,7 @@
       </c>
       <c r="P77" s="1"/>
       <c r="Q77" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R77" s="1" t="s">
         <v>30</v>
@@ -10150,7 +10150,7 @@
         <v>30</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G78" s="1"/>
       <c r="H78" s="1"/>
@@ -10162,18 +10162,18 @@
         <v>437</v>
       </c>
       <c r="L78" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M78" s="1"/>
       <c r="N78" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O78" s="1" t="s">
         <v>438</v>
       </c>
       <c r="P78" s="1"/>
       <c r="Q78" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R78" s="1" t="s">
         <v>30</v>
@@ -10421,13 +10421,13 @@
         <v>27</v>
       </c>
       <c r="G83" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H83" s="1" t="s">
         <v>463</v>
       </c>
       <c r="I83" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J83" s="1"/>
       <c r="K83" s="1"/>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="P85" s="1"/>
       <c r="Q85" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R85" s="1" t="s">
         <v>30</v>
@@ -10700,7 +10700,7 @@
         <v>30</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G88" s="1"/>
       <c r="H88" s="1"/>
@@ -10718,14 +10718,14 @@
         <v>497</v>
       </c>
       <c r="N88" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O88" s="1" t="s">
         <v>498</v>
       </c>
       <c r="P88" s="1"/>
       <c r="Q88" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R88" s="1" t="s">
         <v>30</v>
@@ -10828,7 +10828,7 @@
         <v>293</v>
       </c>
       <c r="L90" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M90" s="1" t="s">
         <v>511</v>
@@ -10881,10 +10881,10 @@
         <v>516</v>
       </c>
       <c r="K91" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L91" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M91" s="1" t="s">
         <v>515</v>
@@ -10897,7 +10897,7 @@
       </c>
       <c r="P91" s="1"/>
       <c r="Q91" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R91" s="1" t="s">
         <v>30</v>
@@ -11255,7 +11255,7 @@
       </c>
       <c r="P97" s="1"/>
       <c r="Q97" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R97" s="1" t="s">
         <v>30</v>
@@ -11356,7 +11356,7 @@
         <v>572</v>
       </c>
       <c r="L99" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M99" s="1"/>
       <c r="N99" s="1" t="s">
@@ -11427,7 +11427,7 @@
         <v>581</v>
       </c>
       <c r="Q100" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R100" s="1" t="s">
         <v>26</v>
@@ -11465,7 +11465,7 @@
         <v>585</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J101" s="1" t="s">
         <v>586</v>
@@ -11487,7 +11487,7 @@
       </c>
       <c r="P101" s="1"/>
       <c r="Q101" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R101" s="1" t="s">
         <v>30</v>
@@ -11601,7 +11601,7 @@
       </c>
       <c r="P103" s="1"/>
       <c r="Q103" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R103" s="1" t="s">
         <v>30</v>
@@ -11651,7 +11651,7 @@
       </c>
       <c r="P104" s="1"/>
       <c r="Q104" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R104" s="1" t="s">
         <v>30</v>
@@ -11744,7 +11744,7 @@
         <v>245</v>
       </c>
       <c r="L106" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M106" s="1" t="s">
         <v>610</v>
@@ -11757,7 +11757,7 @@
       </c>
       <c r="P106" s="1"/>
       <c r="Q106" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R106" s="1" t="s">
         <v>30</v>
@@ -12089,7 +12089,7 @@
         <v>649</v>
       </c>
       <c r="Q112" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R112" s="1" t="s">
         <v>26</v>
@@ -12167,13 +12167,13 @@
         <v>27</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H114" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I114" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J114" s="1" t="s">
         <v>656</v>
@@ -12284,7 +12284,7 @@
         <v>670</v>
       </c>
       <c r="L116" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M116" s="1" t="s">
         <v>667</v>
@@ -12344,7 +12344,7 @@
         <v>245</v>
       </c>
       <c r="L117" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M117" s="1" t="s">
         <v>675</v>
@@ -12400,7 +12400,7 @@
         <v>683</v>
       </c>
       <c r="L118" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M118" s="1" t="s">
         <v>681</v>
@@ -12465,7 +12465,7 @@
       </c>
       <c r="P119" s="1"/>
       <c r="Q119" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R119" s="1" t="s">
         <v>30</v>
@@ -12577,7 +12577,7 @@
       </c>
       <c r="P121" s="1"/>
       <c r="Q121" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R121" s="1" t="s">
         <v>30</v>
@@ -12750,7 +12750,7 @@
         <v>30</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G125" s="1" t="s">
         <v>28</v>
@@ -12774,7 +12774,7 @@
         <v>716</v>
       </c>
       <c r="N125" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O125" s="1" t="s">
         <v>720</v>
@@ -12837,7 +12837,7 @@
       </c>
       <c r="P126" s="1"/>
       <c r="Q126" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R126" s="1" t="s">
         <v>30</v>
@@ -12866,7 +12866,7 @@
         <v>30</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G127" s="1" t="s">
         <v>28</v>
@@ -13014,7 +13014,7 @@
         <v>30</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G130" s="1"/>
       <c r="H130" s="1"/>
@@ -13054,7 +13054,7 @@
         <v>30</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G131" s="1"/>
       <c r="H131" s="1"/>
@@ -13173,7 +13173,7 @@
       </c>
       <c r="P133" s="1"/>
       <c r="Q133" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R133" s="1" t="s">
         <v>30</v>
@@ -13299,7 +13299,7 @@
       </c>
       <c r="P135" s="1"/>
       <c r="Q135" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R135" s="1" t="s">
         <v>26</v>
@@ -13355,7 +13355,7 @@
       </c>
       <c r="P136" s="1"/>
       <c r="Q136" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R136" s="1" t="s">
         <v>30</v>
@@ -13417,7 +13417,7 @@
       </c>
       <c r="P137" s="1"/>
       <c r="Q137" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R137" s="1" t="s">
         <v>30</v>
@@ -13520,7 +13520,7 @@
         <v>791</v>
       </c>
       <c r="L139" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M139" s="1" t="s">
         <v>787</v>
@@ -13701,7 +13701,7 @@
       </c>
       <c r="P142" s="1"/>
       <c r="Q142" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R142" s="1" t="s">
         <v>30</v>
@@ -13850,7 +13850,7 @@
         <v>30</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
@@ -13859,21 +13859,21 @@
         <v>829</v>
       </c>
       <c r="K145" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L145" s="1" t="s">
         <v>830</v>
       </c>
       <c r="M145" s="1"/>
       <c r="N145" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O145" s="1" t="s">
         <v>831</v>
       </c>
       <c r="P145" s="1"/>
       <c r="Q145" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R145" s="1" t="s">
         <v>30</v>
@@ -14047,7 +14047,7 @@
       </c>
       <c r="P148" s="1"/>
       <c r="Q148" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R148" s="1" t="s">
         <v>26</v>
@@ -14200,7 +14200,7 @@
         <v>30</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
@@ -14218,14 +14218,14 @@
         <v>868</v>
       </c>
       <c r="N151" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O151" s="1" t="s">
         <v>869</v>
       </c>
       <c r="P151" s="1"/>
       <c r="Q151" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R151" s="1" t="s">
         <v>30</v>
@@ -14360,7 +14360,7 @@
         <v>59</v>
       </c>
       <c r="L154" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M154" s="1" t="s">
         <v>882</v>
@@ -14407,13 +14407,13 @@
         <v>27</v>
       </c>
       <c r="G155" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H155" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I155" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J155" s="1" t="s">
         <v>888</v>
@@ -14422,7 +14422,7 @@
         <v>59</v>
       </c>
       <c r="L155" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M155" s="1" t="s">
         <v>887</v>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="P155" s="1"/>
       <c r="Q155" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R155" s="1" t="s">
         <v>30</v>
@@ -14738,7 +14738,7 @@
         <v>30</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G162" s="1"/>
       <c r="H162" s="1"/>
@@ -14747,21 +14747,21 @@
         <v>915</v>
       </c>
       <c r="K162" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L162" s="1" t="s">
         <v>203</v>
       </c>
       <c r="M162" s="1"/>
       <c r="N162" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O162" s="1" t="s">
         <v>916</v>
       </c>
       <c r="P162" s="1"/>
       <c r="Q162" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R162" s="1" t="s">
         <v>30</v>
@@ -14971,7 +14971,7 @@
       </c>
       <c r="P166" s="1"/>
       <c r="Q166" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R166" s="1" t="s">
         <v>30</v>
@@ -15017,7 +15017,7 @@
         <v>939</v>
       </c>
       <c r="K167" s="1" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="L167" s="1" t="s">
         <v>940</v>
@@ -15091,7 +15091,7 @@
       </c>
       <c r="P168" s="1"/>
       <c r="Q168" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R168" s="1" t="s">
         <v>30</v>
@@ -15244,7 +15244,7 @@
         <v>962</v>
       </c>
       <c r="L171" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M171" s="1"/>
       <c r="N171" s="1" t="s">
@@ -15297,7 +15297,7 @@
         <v>968</v>
       </c>
       <c r="K172" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L172" s="1" t="s">
         <v>969</v>
@@ -15425,7 +15425,7 @@
         <v>985</v>
       </c>
       <c r="Q174" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R174" s="1" t="s">
         <v>26</v>
@@ -15474,7 +15474,7 @@
         <v>165</v>
       </c>
       <c r="L175" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M175" s="1" t="s">
         <v>993</v>
@@ -15487,7 +15487,7 @@
       </c>
       <c r="P175" s="1"/>
       <c r="Q175" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R175" s="1" t="s">
         <v>30</v>
@@ -15516,7 +15516,7 @@
         <v>30</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
@@ -15528,11 +15528,11 @@
         <v>59</v>
       </c>
       <c r="L176" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M176" s="1"/>
       <c r="N176" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O176" s="1" t="s">
         <v>998</v>
@@ -15667,7 +15667,7 @@
       </c>
       <c r="P178" s="1"/>
       <c r="Q178" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R178" s="1" t="s">
         <v>30</v>
@@ -15699,7 +15699,7 @@
         <v>27</v>
       </c>
       <c r="G179" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H179" s="1" t="s">
         <v>1017</v>
@@ -15727,7 +15727,7 @@
       </c>
       <c r="P179" s="1"/>
       <c r="Q179" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R179" s="1" t="s">
         <v>30</v>
@@ -15758,7 +15758,7 @@
         <v>30</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="G180" s="1" t="s">
         <v>28</v>
@@ -15782,14 +15782,14 @@
         <v>1026</v>
       </c>
       <c r="N180" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="O180" s="1" t="s">
         <v>1027</v>
       </c>
       <c r="P180" s="1"/>
       <c r="Q180" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R180" s="1" t="s">
         <v>30</v>
@@ -15891,7 +15891,7 @@
       </c>
       <c r="P182" s="1"/>
       <c r="Q182" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R182" s="1" t="s">
         <v>26</v>
@@ -15996,7 +15996,7 @@
         <v>1051</v>
       </c>
       <c r="L184" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M184" s="1" t="s">
         <v>1052</v>
@@ -16009,7 +16009,7 @@
       </c>
       <c r="P184" s="1"/>
       <c r="Q184" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R184" s="1" t="s">
         <v>30</v>
@@ -16043,7 +16043,7 @@
         <v>27</v>
       </c>
       <c r="G185" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H185" s="1"/>
       <c r="I185" s="1"/>
@@ -16096,7 +16096,7 @@
         <v>59</v>
       </c>
       <c r="L186" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M186" s="1"/>
       <c r="N186" s="1" t="s">
@@ -16107,7 +16107,7 @@
       </c>
       <c r="P186" s="1"/>
       <c r="Q186" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R186" s="1" t="s">
         <v>30</v>
@@ -16279,7 +16279,7 @@
       </c>
       <c r="P189" s="1"/>
       <c r="Q189" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R189" s="1" t="s">
         <v>30</v>
@@ -16339,7 +16339,7 @@
       </c>
       <c r="P190" s="1"/>
       <c r="Q190" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R190" s="1" t="s">
         <v>30</v>
@@ -16386,7 +16386,7 @@
         <v>1092</v>
       </c>
       <c r="L191" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M191" s="1" t="s">
         <v>1093</v>
@@ -16446,7 +16446,7 @@
         <v>1100</v>
       </c>
       <c r="L192" s="1" t="s">
-        <v>83</v>
+        <v>89</v>
       </c>
       <c r="M192" s="1" t="s">
         <v>1097</v>
@@ -16552,7 +16552,7 @@
         <v>30</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G194" s="1" t="s">
         <v>1110</v>
@@ -16605,13 +16605,13 @@
         <v>27</v>
       </c>
       <c r="G195" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H195" s="1" t="s">
         <v>1117</v>
       </c>
       <c r="I195" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J195" s="1" t="s">
         <v>1118</v>
@@ -16620,7 +16620,7 @@
         <v>1119</v>
       </c>
       <c r="L195" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M195" s="1" t="s">
         <v>1116</v>
@@ -16751,7 +16751,7 @@
       </c>
       <c r="P197" s="1"/>
       <c r="Q197" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R197" s="1" t="s">
         <v>30</v>
@@ -16813,7 +16813,7 @@
       </c>
       <c r="P198" s="1"/>
       <c r="Q198" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R198" s="1" t="s">
         <v>30</v>
@@ -16867,7 +16867,7 @@
       </c>
       <c r="P199" s="1"/>
       <c r="Q199" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R199" s="1" t="s">
         <v>30</v>
@@ -16983,7 +16983,7 @@
       </c>
       <c r="P201" s="1"/>
       <c r="Q201" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R201" s="1" t="s">
         <v>30</v>
@@ -17085,7 +17085,7 @@
       </c>
       <c r="P203" s="1"/>
       <c r="Q203" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R203" s="1" t="s">
         <v>26</v>
@@ -17243,13 +17243,13 @@
         <v>27</v>
       </c>
       <c r="G206" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H206" s="1" t="s">
         <v>1188</v>
       </c>
       <c r="I206" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J206" s="1"/>
       <c r="K206" s="1"/>
@@ -17375,7 +17375,7 @@
       </c>
       <c r="P208" s="1"/>
       <c r="Q208" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R208" s="1" t="s">
         <v>26</v>
@@ -17429,7 +17429,7 @@
       </c>
       <c r="P209" s="1"/>
       <c r="Q209" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R209" s="1" t="s">
         <v>26</v>
@@ -17489,7 +17489,7 @@
       </c>
       <c r="P210" s="1"/>
       <c r="Q210" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R210" s="1" t="s">
         <v>30</v>
@@ -17551,7 +17551,7 @@
       </c>
       <c r="P211" s="1"/>
       <c r="Q211" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R211" s="1" t="s">
         <v>30</v>
@@ -17586,7 +17586,7 @@
         <v>30</v>
       </c>
       <c r="F212" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G212" s="1" t="s">
         <v>1235</v>
@@ -17606,7 +17606,7 @@
         <v>1234</v>
       </c>
       <c r="N212" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O212" s="1" t="s">
         <v>1238</v>
@@ -17648,16 +17648,16 @@
         <v>30</v>
       </c>
       <c r="F213" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I213" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J213" s="1" t="s">
         <v>1236</v>
@@ -17672,7 +17672,7 @@
         <v>1234</v>
       </c>
       <c r="N213" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O213" s="1" t="s">
         <v>1238</v>
@@ -17787,10 +17787,10 @@
         <v>1254</v>
       </c>
       <c r="K215" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="L215" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M215" s="1" t="s">
         <v>1255</v>
@@ -17861,7 +17861,7 @@
       </c>
       <c r="P216" s="1"/>
       <c r="Q216" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R216" s="1" t="s">
         <v>30</v>
@@ -17923,7 +17923,7 @@
       </c>
       <c r="P217" s="1"/>
       <c r="Q217" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R217" s="1" t="s">
         <v>30</v>
@@ -17961,7 +17961,7 @@
         <v>937</v>
       </c>
       <c r="G218" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H218" s="1"/>
       <c r="I218" s="1"/>
@@ -17985,7 +17985,7 @@
       </c>
       <c r="P218" s="1"/>
       <c r="Q218" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R218" s="1" t="s">
         <v>30</v>
@@ -18135,7 +18135,7 @@
         <v>1279</v>
       </c>
       <c r="K221" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L221" s="1" t="s">
         <v>203</v>
@@ -18204,7 +18204,7 @@
         <v>1292</v>
       </c>
       <c r="L222" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M222" s="1" t="s">
         <v>1293</v>
@@ -18264,7 +18264,7 @@
         <v>1300</v>
       </c>
       <c r="L223" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M223" s="1" t="s">
         <v>1301</v>
@@ -18277,7 +18277,7 @@
       </c>
       <c r="P223" s="1"/>
       <c r="Q223" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R223" s="1" t="s">
         <v>30</v>
@@ -18335,7 +18335,7 @@
       </c>
       <c r="P224" s="1"/>
       <c r="Q224" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R224" s="1" t="s">
         <v>26</v>
@@ -18395,7 +18395,7 @@
       </c>
       <c r="P225" s="1"/>
       <c r="Q225" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R225" s="1" t="s">
         <v>26</v>
@@ -18459,7 +18459,7 @@
       </c>
       <c r="P226" s="1"/>
       <c r="Q226" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R226" s="1" t="s">
         <v>30</v>
@@ -18519,7 +18519,7 @@
       </c>
       <c r="P227" s="1"/>
       <c r="Q227" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R227" s="1" t="s">
         <v>30</v>
@@ -18583,7 +18583,7 @@
       </c>
       <c r="P228" s="1"/>
       <c r="Q228" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R228" s="1" t="s">
         <v>30</v>
@@ -18705,7 +18705,7 @@
       </c>
       <c r="P230" s="1"/>
       <c r="Q230" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R230" s="1" t="s">
         <v>30</v>
@@ -18754,7 +18754,7 @@
         <v>165</v>
       </c>
       <c r="L231" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M231" s="1" t="s">
         <v>1358</v>
@@ -18767,7 +18767,7 @@
       </c>
       <c r="P231" s="1"/>
       <c r="Q231" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R231" s="1" t="s">
         <v>30</v>
@@ -18805,13 +18805,13 @@
         <v>27</v>
       </c>
       <c r="G232" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H232" s="1" t="s">
         <v>1364</v>
       </c>
       <c r="I232" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J232" s="1" t="s">
         <v>1365</v>
@@ -18833,7 +18833,7 @@
       </c>
       <c r="P232" s="1"/>
       <c r="Q232" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R232" s="1" t="s">
         <v>30</v>
@@ -18893,7 +18893,7 @@
       </c>
       <c r="P233" s="1"/>
       <c r="Q233" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R233" s="1" t="s">
         <v>30</v>
@@ -18946,7 +18946,7 @@
         <v>670</v>
       </c>
       <c r="L234" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M234" s="1" t="s">
         <v>1381</v>
@@ -18959,7 +18959,7 @@
       </c>
       <c r="P234" s="1"/>
       <c r="Q234" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R234" s="1" t="s">
         <v>30</v>
@@ -19073,7 +19073,7 @@
         <v>1398</v>
       </c>
       <c r="K236" s="1" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="L236" s="1" t="s">
         <v>1399</v>
@@ -19089,7 +19089,7 @@
       </c>
       <c r="P236" s="1"/>
       <c r="Q236" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R236" s="1" t="s">
         <v>30</v>
@@ -19155,7 +19155,7 @@
       </c>
       <c r="P237" s="1"/>
       <c r="Q237" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R237" s="1" t="s">
         <v>30</v>
@@ -19219,7 +19219,7 @@
       </c>
       <c r="P238" s="1"/>
       <c r="Q238" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R238" s="1" t="s">
         <v>30</v>
@@ -19277,7 +19277,7 @@
       </c>
       <c r="P239" s="1"/>
       <c r="Q239" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R239" s="1" t="s">
         <v>30</v>
@@ -19525,7 +19525,7 @@
       </c>
       <c r="P243" s="1"/>
       <c r="Q243" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R243" s="1" t="s">
         <v>30</v>
@@ -19640,7 +19640,7 @@
         <v>1456</v>
       </c>
       <c r="L245" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M245" s="1" t="s">
         <v>1461</v>
@@ -19713,7 +19713,7 @@
       </c>
       <c r="P246" s="1"/>
       <c r="Q246" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R246" s="1" t="s">
         <v>26</v>
@@ -19757,10 +19757,10 @@
         <v>1472</v>
       </c>
       <c r="K247" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="L247" s="1" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="M247" s="1" t="s">
         <v>1471</v>
@@ -19773,7 +19773,7 @@
       </c>
       <c r="P247" s="1"/>
       <c r="Q247" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R247" s="1" t="s">
         <v>30</v>
@@ -19869,13 +19869,13 @@
         <v>27</v>
       </c>
       <c r="G249" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H249" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I249" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J249" s="1" t="s">
         <v>1478</v>
@@ -19959,7 +19959,7 @@
         <v>1492</v>
       </c>
       <c r="Q250" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R250" s="1" t="s">
         <v>30</v>
@@ -20072,7 +20072,7 @@
         <v>293</v>
       </c>
       <c r="L252" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M252" s="1" t="s">
         <v>1505</v>
@@ -20085,7 +20085,7 @@
       </c>
       <c r="P252" s="1"/>
       <c r="Q252" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R252" s="1" t="s">
         <v>30</v>
@@ -20134,7 +20134,7 @@
         <v>293</v>
       </c>
       <c r="L253" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M253" s="1" t="s">
         <v>1505</v>
@@ -20147,7 +20147,7 @@
       </c>
       <c r="P253" s="1"/>
       <c r="Q253" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R253" s="1" t="s">
         <v>30</v>
@@ -20267,7 +20267,7 @@
       </c>
       <c r="P255" s="1"/>
       <c r="Q255" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R255" s="1" t="s">
         <v>30</v>
@@ -20678,7 +20678,7 @@
         <v>1572</v>
       </c>
       <c r="L262" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M262" s="1" t="s">
         <v>1568</v>
@@ -20691,7 +20691,7 @@
       </c>
       <c r="P262" s="1"/>
       <c r="Q262" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R262" s="1" t="s">
         <v>30</v>
@@ -20740,7 +20740,7 @@
         <v>1572</v>
       </c>
       <c r="L263" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M263" s="1" t="s">
         <v>1578</v>
@@ -20753,7 +20753,7 @@
       </c>
       <c r="P263" s="1"/>
       <c r="Q263" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R263" s="1" t="s">
         <v>30</v>
@@ -20800,7 +20800,7 @@
         <v>490</v>
       </c>
       <c r="L264" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M264" s="1" t="s">
         <v>1586</v>
@@ -20813,7 +20813,7 @@
       </c>
       <c r="P264" s="1"/>
       <c r="Q264" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R264" s="1" t="s">
         <v>30</v>
@@ -20913,13 +20913,13 @@
         <v>27</v>
       </c>
       <c r="G266" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H266" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="I266" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J266" s="1" t="s">
         <v>1599</v>
@@ -20941,7 +20941,7 @@
       </c>
       <c r="P266" s="1"/>
       <c r="Q266" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R266" s="1" t="s">
         <v>30</v>
@@ -20988,7 +20988,7 @@
         <v>293</v>
       </c>
       <c r="L267" s="1" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="M267" s="1" t="s">
         <v>1607</v>
@@ -21061,7 +21061,7 @@
       </c>
       <c r="P268" s="1"/>
       <c r="Q268" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R268" s="1" t="s">
         <v>30</v>
@@ -21112,7 +21112,7 @@
         <v>1623</v>
       </c>
       <c r="L269" s="1" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="M269" s="1" t="s">
         <v>1624</v>
@@ -21125,7 +21125,7 @@
       </c>
       <c r="P269" s="1"/>
       <c r="Q269" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R269" s="1" t="s">
         <v>30</v>
@@ -21174,7 +21174,7 @@
         <v>670</v>
       </c>
       <c r="L270" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M270" s="1" t="s">
         <v>1629</v>
@@ -21236,7 +21236,7 @@
         <v>670</v>
       </c>
       <c r="L271" s="1" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="M271" s="1" t="s">
         <v>1629</v>
@@ -21300,7 +21300,7 @@
         <v>59</v>
       </c>
       <c r="L272" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M272" s="1" t="s">
         <v>1641</v>
@@ -21364,7 +21364,7 @@
         <v>59</v>
       </c>
       <c r="L273" s="1" t="s">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="M273" s="1" t="s">
         <v>1648</v>
@@ -21415,13 +21415,13 @@
         <v>209</v>
       </c>
       <c r="G274" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H274" s="1" t="s">
         <v>1657</v>
       </c>
       <c r="I274" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J274" s="1" t="s">
         <v>1658</v>
@@ -21445,7 +21445,7 @@
         <v>1662</v>
       </c>
       <c r="Q274" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R274" s="1" t="s">
         <v>30</v>
@@ -21483,13 +21483,13 @@
         <v>209</v>
       </c>
       <c r="G275" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="H275" s="1" t="s">
         <v>1657</v>
       </c>
       <c r="I275" s="1" t="s">
-        <v>117</v>
+        <v>108</v>
       </c>
       <c r="J275" s="1" t="s">
         <v>1658</v>
@@ -21513,7 +21513,7 @@
         <v>1662</v>
       </c>
       <c r="Q275" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R275" s="1" t="s">
         <v>30</v>
@@ -21573,7 +21573,7 @@
       </c>
       <c r="P276" s="1"/>
       <c r="Q276" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R276" s="1" t="s">
         <v>30</v>
@@ -21637,7 +21637,7 @@
       </c>
       <c r="P277" s="1"/>
       <c r="Q277" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R277" s="1" t="s">
         <v>30</v>
@@ -21701,7 +21701,7 @@
       </c>
       <c r="P278" s="1"/>
       <c r="Q278" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R278" s="1" t="s">
         <v>30</v>
@@ -21761,7 +21761,7 @@
       </c>
       <c r="P279" s="1"/>
       <c r="Q279" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R279" s="1" t="s">
         <v>30</v>
@@ -21881,7 +21881,7 @@
       </c>
       <c r="P281" s="1"/>
       <c r="Q281" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R281" s="1" t="s">
         <v>30</v>
@@ -22007,7 +22007,7 @@
       </c>
       <c r="P283" s="1"/>
       <c r="Q283" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R283" s="1" t="s">
         <v>30</v>
@@ -22183,7 +22183,7 @@
         <v>1742</v>
       </c>
       <c r="Q286" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R286" s="1" t="s">
         <v>30</v>
@@ -22245,7 +22245,7 @@
       </c>
       <c r="P287" s="1"/>
       <c r="Q287" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="R287" s="1" t="s">
         <v>30</v>
@@ -22280,7 +22280,7 @@
         <v>30</v>
       </c>
       <c r="F288" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G288" s="1" t="s">
         <v>1757</v>
@@ -22294,20 +22294,20 @@
         <v>1759</v>
       </c>
       <c r="L288" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M288" s="1" t="s">
         <v>1756</v>
       </c>
       <c r="N288" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O288" s="1" t="s">
         <v>1760</v>
       </c>
       <c r="P288" s="1"/>
       <c r="Q288" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R288" s="1" t="s">
         <v>30</v>
@@ -22340,7 +22340,7 @@
         <v>30</v>
       </c>
       <c r="F289" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="G289" s="1"/>
       <c r="H289" s="1"/>
@@ -22352,20 +22352,20 @@
         <v>1764</v>
       </c>
       <c r="L289" s="1" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="M289" s="1" t="s">
         <v>1756</v>
       </c>
       <c r="N289" s="1" t="s">
-        <v>192</v>
+        <v>185</v>
       </c>
       <c r="O289" s="1" t="s">
         <v>1765</v>
       </c>
       <c r="P289" s="1"/>
       <c r="Q289" s="1" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="R289" s="1" t="s">
         <v>30</v>
